--- a/ksoft/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
@@ -81561,13 +81561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE98A14-2A3B-4F15-A77F-81EDD7D64253}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2ED05BF-EE73-447B-A551-F22A20E31D23}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3F42560-5962-46D9-B4B9-2BB6A72F6979}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36C746D-85B2-4B9A-B3FB-088C96A8F37F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB76562B-8B66-4A06-9DE6-5B9938CBBEA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65453D56-C527-4471-B1C3-B15C2141C8EB}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CC0407-04092024-144019.xlsx
@@ -81561,13 +81561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2ED05BF-EE73-447B-A551-F22A20E31D23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE98A14-2A3B-4F15-A77F-81EDD7D64253}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36C746D-85B2-4B9A-B3FB-088C96A8F37F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3F42560-5962-46D9-B4B9-2BB6A72F6979}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65453D56-C527-4471-B1C3-B15C2141C8EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB76562B-8B66-4A06-9DE6-5B9938CBBEA3}"/>
 </file>